--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/COLORADO_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/COLORADO_2020.xlsx
@@ -643,7 +643,7 @@
         <v>1</v>
       </c>
       <c r="D16">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="17">
@@ -679,7 +679,7 @@
         <v>1</v>
       </c>
       <c r="D18">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="19">
@@ -697,7 +697,7 @@
         <v>1</v>
       </c>
       <c r="D19">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="20">
@@ -787,7 +787,7 @@
         <v>1</v>
       </c>
       <c r="D24">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="25">
@@ -841,7 +841,7 @@
         <v>1</v>
       </c>
       <c r="D27">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="28">
@@ -859,7 +859,7 @@
         <v>1</v>
       </c>
       <c r="D28">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="29">
@@ -877,7 +877,7 @@
         <v>1</v>
       </c>
       <c r="D29">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="30">
@@ -949,7 +949,7 @@
         <v>1</v>
       </c>
       <c r="D33">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="34">
@@ -967,7 +967,7 @@
         <v>1</v>
       </c>
       <c r="D34">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="35">
@@ -985,7 +985,7 @@
         <v>1</v>
       </c>
       <c r="D35">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="36">
@@ -1021,7 +1021,7 @@
         <v>1</v>
       </c>
       <c r="D37">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="38">
@@ -1129,7 +1129,7 @@
         <v>1</v>
       </c>
       <c r="D43">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="44">
@@ -1147,7 +1147,7 @@
         <v>1</v>
       </c>
       <c r="D44">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="45">
@@ -1165,7 +1165,7 @@
         <v>1</v>
       </c>
       <c r="D45">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="46">
@@ -1309,7 +1309,7 @@
         <v>1</v>
       </c>
       <c r="D53">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="54">
@@ -1327,7 +1327,7 @@
         <v>1</v>
       </c>
       <c r="D54">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="55">
@@ -1345,7 +1345,7 @@
         <v>1</v>
       </c>
       <c r="D55">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="56">
@@ -1453,7 +1453,7 @@
         <v>1</v>
       </c>
       <c r="D61">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="62">
@@ -1507,7 +1507,7 @@
         <v>1</v>
       </c>
       <c r="D64">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="65">
@@ -1525,7 +1525,7 @@
         <v>1</v>
       </c>
       <c r="D65">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="66">
@@ -1597,7 +1597,7 @@
         <v>1</v>
       </c>
       <c r="D69">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="70">
@@ -1651,7 +1651,7 @@
         <v>1</v>
       </c>
       <c r="D72">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="73">
@@ -1669,7 +1669,7 @@
         <v>1</v>
       </c>
       <c r="D73">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="74">
@@ -1705,7 +1705,7 @@
         <v>1</v>
       </c>
       <c r="D75">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="76">
@@ -1723,7 +1723,7 @@
         <v>10</v>
       </c>
       <c r="D76">
-        <v>0.0009378223764419019</v>
+        <v>0.000937822376441902</v>
       </c>
     </row>
     <row r="77">
@@ -2101,7 +2101,7 @@
         <v>1</v>
       </c>
       <c r="D97">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="98">
@@ -2137,7 +2137,7 @@
         <v>10</v>
       </c>
       <c r="D99">
-        <v>0.0009378223764419019</v>
+        <v>0.000937822376441902</v>
       </c>
     </row>
     <row r="100">
@@ -2155,7 +2155,7 @@
         <v>10</v>
       </c>
       <c r="D100">
-        <v>0.0009378223764419019</v>
+        <v>0.000937822376441902</v>
       </c>
     </row>
     <row r="101">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Guerero</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="C104">
@@ -2353,7 +2353,7 @@
         <v>1</v>
       </c>
       <c r="D111">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="112">
@@ -2389,7 +2389,7 @@
         <v>1</v>
       </c>
       <c r="D113">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="114">
@@ -2425,7 +2425,7 @@
         <v>1</v>
       </c>
       <c r="D115">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="116">
@@ -2533,7 +2533,7 @@
         <v>10</v>
       </c>
       <c r="D121">
-        <v>0.0009378223764419019</v>
+        <v>0.000937822376441902</v>
       </c>
     </row>
     <row r="122">
@@ -2569,7 +2569,7 @@
         <v>10</v>
       </c>
       <c r="D123">
-        <v>0.0009378223764419019</v>
+        <v>0.000937822376441902</v>
       </c>
     </row>
     <row r="124">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Praxedis G. Guerero</t>
+          <t>Praxedis G. Guerrero</t>
         </is>
       </c>
       <c r="C125">
@@ -2623,7 +2623,7 @@
         <v>10</v>
       </c>
       <c r="D126">
-        <v>0.0009378223764419019</v>
+        <v>0.000937822376441902</v>
       </c>
     </row>
     <row r="127">
@@ -2641,7 +2641,7 @@
         <v>1</v>
       </c>
       <c r="D127">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="128">
@@ -2695,7 +2695,7 @@
         <v>1</v>
       </c>
       <c r="D130">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="131">
@@ -2749,7 +2749,7 @@
         <v>10</v>
       </c>
       <c r="D133">
-        <v>0.0009378223764419019</v>
+        <v>0.000937822376441902</v>
       </c>
     </row>
     <row r="134">
@@ -2875,7 +2875,7 @@
         <v>1</v>
       </c>
       <c r="D140">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="141">
@@ -2911,7 +2911,7 @@
         <v>1</v>
       </c>
       <c r="D142">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="143">
@@ -2922,14 +2922,14 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C143">
         <v>1</v>
       </c>
       <c r="D143">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="144">
@@ -2965,7 +2965,7 @@
         <v>1</v>
       </c>
       <c r="D145">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="146">
@@ -3037,7 +3037,7 @@
         <v>1</v>
       </c>
       <c r="D149">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="150">
@@ -3055,7 +3055,7 @@
         <v>1</v>
       </c>
       <c r="D150">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="151">
@@ -3109,7 +3109,7 @@
         <v>1</v>
       </c>
       <c r="D153">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="154">
@@ -3181,7 +3181,7 @@
         <v>1</v>
       </c>
       <c r="D157">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="158">
@@ -3235,7 +3235,7 @@
         <v>1</v>
       </c>
       <c r="D160">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="161">
@@ -3379,7 +3379,7 @@
         <v>1</v>
       </c>
       <c r="D168">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="169">
@@ -3505,7 +3505,7 @@
         <v>1</v>
       </c>
       <c r="D175">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="176">
@@ -3577,7 +3577,7 @@
         <v>1</v>
       </c>
       <c r="D179">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="180">
@@ -3696,14 +3696,14 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C186">
         <v>1</v>
       </c>
       <c r="D186">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="187">
@@ -3937,7 +3937,7 @@
         <v>10</v>
       </c>
       <c r="D199">
-        <v>0.0009378223764419019</v>
+        <v>0.000937822376441902</v>
       </c>
     </row>
     <row r="200">
@@ -4153,7 +4153,7 @@
         <v>1</v>
       </c>
       <c r="D211">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="212">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C215">
@@ -4279,7 +4279,7 @@
         <v>1</v>
       </c>
       <c r="D218">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="219">
@@ -4423,7 +4423,7 @@
         <v>1</v>
       </c>
       <c r="D226">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="227">
@@ -4495,7 +4495,7 @@
         <v>1</v>
       </c>
       <c r="D230">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="231">
@@ -4549,7 +4549,7 @@
         <v>1</v>
       </c>
       <c r="D233">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="234">
@@ -4585,7 +4585,7 @@
         <v>1</v>
       </c>
       <c r="D235">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="236">
@@ -4639,7 +4639,7 @@
         <v>1</v>
       </c>
       <c r="D238">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="239">
@@ -4675,7 +4675,7 @@
         <v>1</v>
       </c>
       <c r="D240">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="241">
@@ -4783,7 +4783,7 @@
         <v>1</v>
       </c>
       <c r="D246">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="247">
@@ -4819,7 +4819,7 @@
         <v>1</v>
       </c>
       <c r="D248">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="249">
@@ -4837,7 +4837,7 @@
         <v>1</v>
       </c>
       <c r="D249">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="250">
@@ -4981,7 +4981,7 @@
         <v>1</v>
       </c>
       <c r="D257">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="258">
@@ -5017,7 +5017,7 @@
         <v>1</v>
       </c>
       <c r="D259">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="260">
@@ -5053,7 +5053,7 @@
         <v>1</v>
       </c>
       <c r="D261">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="262">
@@ -5089,7 +5089,7 @@
         <v>10</v>
       </c>
       <c r="D263">
-        <v>0.0009378223764419019</v>
+        <v>0.000937822376441902</v>
       </c>
     </row>
     <row r="264">
@@ -5107,7 +5107,7 @@
         <v>1</v>
       </c>
       <c r="D264">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="265">
@@ -5125,7 +5125,7 @@
         <v>1</v>
       </c>
       <c r="D265">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="266">
@@ -5215,7 +5215,7 @@
         <v>1</v>
       </c>
       <c r="D270">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="271">
@@ -5251,7 +5251,7 @@
         <v>1</v>
       </c>
       <c r="D272">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="273">
@@ -5287,7 +5287,7 @@
         <v>1</v>
       </c>
       <c r="D274">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="275">
@@ -5377,7 +5377,7 @@
         <v>1</v>
       </c>
       <c r="D279">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="280">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C281">
@@ -5503,7 +5503,7 @@
         <v>1</v>
       </c>
       <c r="D286">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="287">
@@ -5568,14 +5568,14 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C290">
         <v>10</v>
       </c>
       <c r="D290">
-        <v>0.0009378223764419019</v>
+        <v>0.000937822376441902</v>
       </c>
     </row>
     <row r="291">
@@ -5683,7 +5683,7 @@
         <v>1</v>
       </c>
       <c r="D296">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="297">
@@ -5719,7 +5719,7 @@
         <v>10</v>
       </c>
       <c r="D298">
-        <v>0.0009378223764419019</v>
+        <v>0.000937822376441902</v>
       </c>
     </row>
     <row r="299">
@@ -5737,7 +5737,7 @@
         <v>1</v>
       </c>
       <c r="D299">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="300">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C300">
@@ -5899,7 +5899,7 @@
         <v>1</v>
       </c>
       <c r="D308">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="309">
@@ -5917,7 +5917,7 @@
         <v>1</v>
       </c>
       <c r="D309">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="310">
@@ -6151,7 +6151,7 @@
         <v>10</v>
       </c>
       <c r="D322">
-        <v>0.0009378223764419019</v>
+        <v>0.000937822376441902</v>
       </c>
     </row>
     <row r="323">
@@ -6187,7 +6187,7 @@
         <v>1</v>
       </c>
       <c r="D324">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="325">
@@ -6277,7 +6277,7 @@
         <v>105</v>
       </c>
       <c r="D329">
-        <v>0.009847134952639971</v>
+        <v>0.009847134952639973</v>
       </c>
     </row>
     <row r="330">
@@ -6331,7 +6331,7 @@
         <v>10</v>
       </c>
       <c r="D332">
-        <v>0.0009378223764419019</v>
+        <v>0.000937822376441902</v>
       </c>
     </row>
     <row r="333">
@@ -6637,7 +6637,7 @@
         <v>1</v>
       </c>
       <c r="D349">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="350">
@@ -6979,7 +6979,7 @@
         <v>1</v>
       </c>
       <c r="D368">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="369">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Tixtla De Guerero</t>
+          <t>Tixtla De Guerrero</t>
         </is>
       </c>
       <c r="C381">
@@ -7393,7 +7393,7 @@
         <v>1</v>
       </c>
       <c r="D391">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="392">
@@ -7429,7 +7429,7 @@
         <v>1</v>
       </c>
       <c r="D393">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="394">
@@ -7483,7 +7483,7 @@
         <v>1</v>
       </c>
       <c r="D396">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="397">
@@ -7537,7 +7537,7 @@
         <v>1</v>
       </c>
       <c r="D399">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="400">
@@ -7609,7 +7609,7 @@
         <v>1</v>
       </c>
       <c r="D403">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="404">
@@ -7627,7 +7627,7 @@
         <v>1</v>
       </c>
       <c r="D404">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="405">
@@ -7681,7 +7681,7 @@
         <v>1</v>
       </c>
       <c r="D407">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="408">
@@ -7735,7 +7735,7 @@
         <v>1</v>
       </c>
       <c r="D410">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="411">
@@ -7789,7 +7789,7 @@
         <v>1</v>
       </c>
       <c r="D413">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="414">
@@ -7807,7 +7807,7 @@
         <v>1</v>
       </c>
       <c r="D414">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="415">
@@ -7825,7 +7825,7 @@
         <v>1</v>
       </c>
       <c r="D415">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="416">
@@ -7861,7 +7861,7 @@
         <v>1</v>
       </c>
       <c r="D417">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="418">
@@ -7879,7 +7879,7 @@
         <v>1</v>
       </c>
       <c r="D418">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="419">
@@ -7890,7 +7890,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Tepehuacan De Guerero</t>
+          <t>Tepehuacan De Guerrero</t>
         </is>
       </c>
       <c r="C419">
@@ -7915,7 +7915,7 @@
         <v>1</v>
       </c>
       <c r="D420">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="421">
@@ -7951,7 +7951,7 @@
         <v>1</v>
       </c>
       <c r="D422">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="423">
@@ -7987,7 +7987,7 @@
         <v>1</v>
       </c>
       <c r="D424">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="425">
@@ -8059,7 +8059,7 @@
         <v>1</v>
       </c>
       <c r="D428">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="429">
@@ -8131,7 +8131,7 @@
         <v>1</v>
       </c>
       <c r="D432">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="433">
@@ -8149,7 +8149,7 @@
         <v>1</v>
       </c>
       <c r="D433">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="434">
@@ -8257,7 +8257,7 @@
         <v>1</v>
       </c>
       <c r="D439">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="440">
@@ -8293,7 +8293,7 @@
         <v>1</v>
       </c>
       <c r="D441">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="442">
@@ -8329,7 +8329,7 @@
         <v>1</v>
       </c>
       <c r="D443">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="444">
@@ -8365,7 +8365,7 @@
         <v>1</v>
       </c>
       <c r="D445">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="446">
@@ -8383,7 +8383,7 @@
         <v>1</v>
       </c>
       <c r="D446">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="447">
@@ -8455,7 +8455,7 @@
         <v>1</v>
       </c>
       <c r="D450">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="451">
@@ -8473,7 +8473,7 @@
         <v>1</v>
       </c>
       <c r="D451">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="452">
@@ -8491,7 +8491,7 @@
         <v>1</v>
       </c>
       <c r="D452">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="453">
@@ -8599,7 +8599,7 @@
         <v>1</v>
       </c>
       <c r="D458">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="459">
@@ -8635,7 +8635,7 @@
         <v>10</v>
       </c>
       <c r="D460">
-        <v>0.0009378223764419019</v>
+        <v>0.000937822376441902</v>
       </c>
     </row>
     <row r="461">
@@ -8671,7 +8671,7 @@
         <v>1</v>
       </c>
       <c r="D462">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="463">
@@ -8779,7 +8779,7 @@
         <v>1</v>
       </c>
       <c r="D468">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="469">
@@ -8869,7 +8869,7 @@
         <v>1</v>
       </c>
       <c r="D473">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="474">
@@ -8887,7 +8887,7 @@
         <v>1</v>
       </c>
       <c r="D474">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="475">
@@ -9013,7 +9013,7 @@
         <v>1</v>
       </c>
       <c r="D481">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="482">
@@ -9211,7 +9211,7 @@
         <v>10</v>
       </c>
       <c r="D492">
-        <v>0.0009378223764419019</v>
+        <v>0.000937822376441902</v>
       </c>
     </row>
     <row r="493">
@@ -9265,7 +9265,7 @@
         <v>1</v>
       </c>
       <c r="D495">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="496">
@@ -9409,7 +9409,7 @@
         <v>1</v>
       </c>
       <c r="D503">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="504">
@@ -9463,7 +9463,7 @@
         <v>1</v>
       </c>
       <c r="D506">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="507">
@@ -9474,7 +9474,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C507">
@@ -9499,7 +9499,7 @@
         <v>1</v>
       </c>
       <c r="D508">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="509">
@@ -9517,7 +9517,7 @@
         <v>10</v>
       </c>
       <c r="D509">
-        <v>0.0009378223764419019</v>
+        <v>0.000937822376441902</v>
       </c>
     </row>
     <row r="510">
@@ -9607,7 +9607,7 @@
         <v>1</v>
       </c>
       <c r="D514">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="515">
@@ -9697,7 +9697,7 @@
         <v>1</v>
       </c>
       <c r="D519">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="520">
@@ -9715,7 +9715,7 @@
         <v>1</v>
       </c>
       <c r="D520">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="521">
@@ -9733,7 +9733,7 @@
         <v>1</v>
       </c>
       <c r="D521">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="522">
@@ -9823,7 +9823,7 @@
         <v>1</v>
       </c>
       <c r="D526">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="527">
@@ -9877,7 +9877,7 @@
         <v>1</v>
       </c>
       <c r="D529">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="530">
@@ -9895,7 +9895,7 @@
         <v>1</v>
       </c>
       <c r="D530">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="531">
@@ -9931,7 +9931,7 @@
         <v>1</v>
       </c>
       <c r="D532">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="533">
@@ -9949,7 +9949,7 @@
         <v>10</v>
       </c>
       <c r="D533">
-        <v>0.0009378223764419019</v>
+        <v>0.000937822376441902</v>
       </c>
     </row>
     <row r="534">
@@ -10003,7 +10003,7 @@
         <v>1</v>
       </c>
       <c r="D536">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="537">
@@ -10057,7 +10057,7 @@
         <v>1</v>
       </c>
       <c r="D539">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="540">
@@ -10093,7 +10093,7 @@
         <v>1</v>
       </c>
       <c r="D541">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="542">
@@ -10111,7 +10111,7 @@
         <v>1</v>
       </c>
       <c r="D542">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="543">
@@ -10183,7 +10183,7 @@
         <v>1</v>
       </c>
       <c r="D546">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="547">
@@ -10237,7 +10237,7 @@
         <v>1</v>
       </c>
       <c r="D549">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="550">
@@ -10291,7 +10291,7 @@
         <v>1</v>
       </c>
       <c r="D552">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="553">
@@ -10309,7 +10309,7 @@
         <v>1</v>
       </c>
       <c r="D553">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="554">
@@ -10543,7 +10543,7 @@
         <v>1</v>
       </c>
       <c r="D566">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="567">
@@ -10633,7 +10633,7 @@
         <v>1</v>
       </c>
       <c r="D571">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="572">
@@ -10741,7 +10741,7 @@
         <v>1</v>
       </c>
       <c r="D577">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="578">
@@ -10759,7 +10759,7 @@
         <v>1</v>
       </c>
       <c r="D578">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="579">
@@ -10795,7 +10795,7 @@
         <v>10</v>
       </c>
       <c r="D580">
-        <v>0.0009378223764419019</v>
+        <v>0.000937822376441902</v>
       </c>
     </row>
     <row r="581">
@@ -10831,7 +10831,7 @@
         <v>10</v>
       </c>
       <c r="D582">
-        <v>0.0009378223764419019</v>
+        <v>0.000937822376441902</v>
       </c>
     </row>
     <row r="583">
@@ -10849,7 +10849,7 @@
         <v>1</v>
       </c>
       <c r="D583">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="584">
@@ -10975,7 +10975,7 @@
         <v>1</v>
       </c>
       <c r="D590">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="591">
@@ -11083,7 +11083,7 @@
         <v>1</v>
       </c>
       <c r="D596">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="597">
@@ -11191,7 +11191,7 @@
         <v>1</v>
       </c>
       <c r="D602">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="603">
@@ -11209,7 +11209,7 @@
         <v>10</v>
       </c>
       <c r="D603">
-        <v>0.0009378223764419019</v>
+        <v>0.000937822376441902</v>
       </c>
     </row>
     <row r="604">
@@ -11263,7 +11263,7 @@
         <v>1</v>
       </c>
       <c r="D606">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="607">
@@ -11407,7 +11407,7 @@
         <v>1</v>
       </c>
       <c r="D614">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="615">
@@ -11443,7 +11443,7 @@
         <v>1</v>
       </c>
       <c r="D616">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="617">
@@ -11497,7 +11497,7 @@
         <v>1</v>
       </c>
       <c r="D619">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="620">
@@ -11677,7 +11677,7 @@
         <v>1</v>
       </c>
       <c r="D629">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="630">
@@ -11767,7 +11767,7 @@
         <v>1</v>
       </c>
       <c r="D634">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="635">
@@ -11875,7 +11875,7 @@
         <v>1</v>
       </c>
       <c r="D640">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="641">
@@ -11911,7 +11911,7 @@
         <v>1</v>
       </c>
       <c r="D642">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="643">
@@ -11965,7 +11965,7 @@
         <v>1</v>
       </c>
       <c r="D645">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="646">
@@ -12037,7 +12037,7 @@
         <v>1</v>
       </c>
       <c r="D649">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="650">
@@ -12055,7 +12055,7 @@
         <v>1</v>
       </c>
       <c r="D650">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="651">
@@ -12109,7 +12109,7 @@
         <v>1</v>
       </c>
       <c r="D653">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="654">
@@ -12163,7 +12163,7 @@
         <v>1</v>
       </c>
       <c r="D656">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="657">
@@ -12181,7 +12181,7 @@
         <v>1</v>
       </c>
       <c r="D657">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="658">
@@ -12235,7 +12235,7 @@
         <v>1</v>
       </c>
       <c r="D660">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="661">
@@ -12253,7 +12253,7 @@
         <v>1</v>
       </c>
       <c r="D661">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="662">
@@ -12307,7 +12307,7 @@
         <v>1</v>
       </c>
       <c r="D664">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="665">
@@ -12325,7 +12325,7 @@
         <v>1</v>
       </c>
       <c r="D665">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="666">
@@ -12408,14 +12408,14 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Putla Villa De Guerero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C670">
         <v>1</v>
       </c>
       <c r="D670">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="671">
@@ -12433,7 +12433,7 @@
         <v>1</v>
       </c>
       <c r="D671">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="672">
@@ -12487,7 +12487,7 @@
         <v>1</v>
       </c>
       <c r="D674">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="675">
@@ -12505,7 +12505,7 @@
         <v>1</v>
       </c>
       <c r="D675">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="676">
@@ -12523,7 +12523,7 @@
         <v>1</v>
       </c>
       <c r="D676">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="677">
@@ -12559,7 +12559,7 @@
         <v>1</v>
       </c>
       <c r="D678">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="679">
@@ -12577,7 +12577,7 @@
         <v>1</v>
       </c>
       <c r="D679">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="680">
@@ -12595,7 +12595,7 @@
         <v>1</v>
       </c>
       <c r="D680">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="681">
@@ -12613,7 +12613,7 @@
         <v>1</v>
       </c>
       <c r="D681">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="682">
@@ -12631,7 +12631,7 @@
         <v>1</v>
       </c>
       <c r="D682">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="683">
@@ -12649,7 +12649,7 @@
         <v>1</v>
       </c>
       <c r="D683">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="684">
@@ -12667,7 +12667,7 @@
         <v>1</v>
       </c>
       <c r="D684">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="685">
@@ -12703,7 +12703,7 @@
         <v>1</v>
       </c>
       <c r="D686">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="687">
@@ -12739,7 +12739,7 @@
         <v>1</v>
       </c>
       <c r="D688">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="689">
@@ -12793,7 +12793,7 @@
         <v>1</v>
       </c>
       <c r="D691">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="692">
@@ -12811,7 +12811,7 @@
         <v>1</v>
       </c>
       <c r="D692">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="693">
@@ -12865,7 +12865,7 @@
         <v>1</v>
       </c>
       <c r="D695">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="696">
@@ -12883,7 +12883,7 @@
         <v>1</v>
       </c>
       <c r="D696">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="697">
@@ -12901,7 +12901,7 @@
         <v>1</v>
       </c>
       <c r="D697">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="698">
@@ -12919,7 +12919,7 @@
         <v>1</v>
       </c>
       <c r="D698">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="699">
@@ -12955,7 +12955,7 @@
         <v>1</v>
       </c>
       <c r="D700">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="701">
@@ -12973,7 +12973,7 @@
         <v>1</v>
       </c>
       <c r="D701">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="702">
@@ -12991,7 +12991,7 @@
         <v>1</v>
       </c>
       <c r="D702">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="703">
@@ -13009,7 +13009,7 @@
         <v>1</v>
       </c>
       <c r="D703">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="704">
@@ -13027,7 +13027,7 @@
         <v>1</v>
       </c>
       <c r="D704">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="705">
@@ -13045,7 +13045,7 @@
         <v>1</v>
       </c>
       <c r="D705">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="706">
@@ -13110,14 +13110,14 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C709">
         <v>1</v>
       </c>
       <c r="D709">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="710">
@@ -13128,14 +13128,14 @@
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C710">
         <v>1</v>
       </c>
       <c r="D710">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="711">
@@ -13189,7 +13189,7 @@
         <v>1</v>
       </c>
       <c r="D713">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="714">
@@ -13207,7 +13207,7 @@
         <v>1</v>
       </c>
       <c r="D714">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="715">
@@ -13225,7 +13225,7 @@
         <v>1</v>
       </c>
       <c r="D715">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="716">
@@ -13261,7 +13261,7 @@
         <v>1</v>
       </c>
       <c r="D717">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="718">
@@ -13279,7 +13279,7 @@
         <v>1</v>
       </c>
       <c r="D718">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="719">
@@ -13297,7 +13297,7 @@
         <v>1</v>
       </c>
       <c r="D719">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="720">
@@ -13315,7 +13315,7 @@
         <v>1</v>
       </c>
       <c r="D720">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="721">
@@ -13351,7 +13351,7 @@
         <v>1</v>
       </c>
       <c r="D722">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="723">
@@ -13387,7 +13387,7 @@
         <v>1</v>
       </c>
       <c r="D724">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="725">
@@ -13405,7 +13405,7 @@
         <v>1</v>
       </c>
       <c r="D725">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="726">
@@ -13477,7 +13477,7 @@
         <v>1</v>
       </c>
       <c r="D729">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="730">
@@ -13495,7 +13495,7 @@
         <v>1</v>
       </c>
       <c r="D730">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="731">
@@ -13513,7 +13513,7 @@
         <v>1</v>
       </c>
       <c r="D731">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="732">
@@ -13531,7 +13531,7 @@
         <v>1</v>
       </c>
       <c r="D732">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="733">
@@ -13585,7 +13585,7 @@
         <v>1</v>
       </c>
       <c r="D735">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="736">
@@ -13639,7 +13639,7 @@
         <v>1</v>
       </c>
       <c r="D738">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="739">
@@ -13657,7 +13657,7 @@
         <v>1</v>
       </c>
       <c r="D739">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="740">
@@ -13693,7 +13693,7 @@
         <v>1</v>
       </c>
       <c r="D741">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="742">
@@ -13765,7 +13765,7 @@
         <v>1</v>
       </c>
       <c r="D745">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="746">
@@ -13783,7 +13783,7 @@
         <v>1</v>
       </c>
       <c r="D746">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="747">
@@ -13837,7 +13837,7 @@
         <v>1</v>
       </c>
       <c r="D749">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="750">
@@ -13855,7 +13855,7 @@
         <v>1</v>
       </c>
       <c r="D750">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="751">
@@ -13873,7 +13873,7 @@
         <v>1</v>
       </c>
       <c r="D751">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="752">
@@ -13891,7 +13891,7 @@
         <v>1</v>
       </c>
       <c r="D752">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="753">
@@ -13909,7 +13909,7 @@
         <v>1</v>
       </c>
       <c r="D753">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="754">
@@ -13963,7 +13963,7 @@
         <v>1</v>
       </c>
       <c r="D756">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="757">
@@ -13999,7 +13999,7 @@
         <v>1</v>
       </c>
       <c r="D758">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="759">
@@ -14017,7 +14017,7 @@
         <v>1</v>
       </c>
       <c r="D759">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="760">
@@ -14089,7 +14089,7 @@
         <v>1</v>
       </c>
       <c r="D763">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="764">
@@ -14215,7 +14215,7 @@
         <v>1</v>
       </c>
       <c r="D770">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="771">
@@ -14233,7 +14233,7 @@
         <v>1</v>
       </c>
       <c r="D771">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="772">
@@ -14269,7 +14269,7 @@
         <v>1</v>
       </c>
       <c r="D773">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="774">
@@ -14287,7 +14287,7 @@
         <v>1</v>
       </c>
       <c r="D774">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="775">
@@ -14305,7 +14305,7 @@
         <v>1</v>
       </c>
       <c r="D775">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="776">
@@ -14323,7 +14323,7 @@
         <v>1</v>
       </c>
       <c r="D776">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="777">
@@ -14359,7 +14359,7 @@
         <v>1</v>
       </c>
       <c r="D778">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="779">
@@ -14449,7 +14449,7 @@
         <v>1</v>
       </c>
       <c r="D783">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="784">
@@ -14467,7 +14467,7 @@
         <v>1</v>
       </c>
       <c r="D784">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="785">
@@ -14478,14 +14478,14 @@
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>Ixcamilpa De Guerero</t>
+          <t>Ixcamilpa De Guerrero</t>
         </is>
       </c>
       <c r="C785">
         <v>1</v>
       </c>
       <c r="D785">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="786">
@@ -14521,7 +14521,7 @@
         <v>1</v>
       </c>
       <c r="D787">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="788">
@@ -14539,7 +14539,7 @@
         <v>1</v>
       </c>
       <c r="D788">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="789">
@@ -14575,7 +14575,7 @@
         <v>1</v>
       </c>
       <c r="D790">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="791">
@@ -14611,7 +14611,7 @@
         <v>1</v>
       </c>
       <c r="D792">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="793">
@@ -14647,7 +14647,7 @@
         <v>1</v>
       </c>
       <c r="D794">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="795">
@@ -14683,7 +14683,7 @@
         <v>1</v>
       </c>
       <c r="D796">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="797">
@@ -14701,7 +14701,7 @@
         <v>1</v>
       </c>
       <c r="D797">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="798">
@@ -14755,7 +14755,7 @@
         <v>1</v>
       </c>
       <c r="D800">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="801">
@@ -14827,7 +14827,7 @@
         <v>1</v>
       </c>
       <c r="D804">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="805">
@@ -14863,7 +14863,7 @@
         <v>1</v>
       </c>
       <c r="D806">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="807">
@@ -14881,7 +14881,7 @@
         <v>1</v>
       </c>
       <c r="D807">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="808">
@@ -15043,7 +15043,7 @@
         <v>1</v>
       </c>
       <c r="D816">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="817">
@@ -15061,7 +15061,7 @@
         <v>1</v>
       </c>
       <c r="D817">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="818">
@@ -15169,7 +15169,7 @@
         <v>10</v>
       </c>
       <c r="D823">
-        <v>0.0009378223764419019</v>
+        <v>0.000937822376441902</v>
       </c>
     </row>
     <row r="824">
@@ -15205,7 +15205,7 @@
         <v>1</v>
       </c>
       <c r="D825">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="826">
@@ -15277,7 +15277,7 @@
         <v>1</v>
       </c>
       <c r="D829">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="830">
@@ -15295,7 +15295,7 @@
         <v>1</v>
       </c>
       <c r="D830">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="831">
@@ -15331,7 +15331,7 @@
         <v>1</v>
       </c>
       <c r="D832">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="833">
@@ -15349,7 +15349,7 @@
         <v>1</v>
       </c>
       <c r="D833">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="834">
@@ -15378,7 +15378,7 @@
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C835">
@@ -15475,7 +15475,7 @@
         <v>1</v>
       </c>
       <c r="D840">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="841">
@@ -15493,7 +15493,7 @@
         <v>1</v>
       </c>
       <c r="D841">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="842">
@@ -15529,7 +15529,7 @@
         <v>1</v>
       </c>
       <c r="D843">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="844">
@@ -15565,7 +15565,7 @@
         <v>1</v>
       </c>
       <c r="D845">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="846">
@@ -15601,7 +15601,7 @@
         <v>1</v>
       </c>
       <c r="D847">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="848">
@@ -15637,7 +15637,7 @@
         <v>1</v>
       </c>
       <c r="D849">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="850">
@@ -15709,7 +15709,7 @@
         <v>1</v>
       </c>
       <c r="D853">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="854">
@@ -15817,7 +15817,7 @@
         <v>1</v>
       </c>
       <c r="D859">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="860">
@@ -15853,7 +15853,7 @@
         <v>1</v>
       </c>
       <c r="D861">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="862">
@@ -15871,7 +15871,7 @@
         <v>1</v>
       </c>
       <c r="D862">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="863">
@@ -15889,7 +15889,7 @@
         <v>1</v>
       </c>
       <c r="D863">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="864">
@@ -15961,7 +15961,7 @@
         <v>1</v>
       </c>
       <c r="D867">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="868">
@@ -15997,7 +15997,7 @@
         <v>1</v>
       </c>
       <c r="D869">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="870">
@@ -16069,7 +16069,7 @@
         <v>1</v>
       </c>
       <c r="D873">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="874">
@@ -16177,7 +16177,7 @@
         <v>1</v>
       </c>
       <c r="D879">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="880">
@@ -16213,7 +16213,7 @@
         <v>10</v>
       </c>
       <c r="D881">
-        <v>0.0009378223764419019</v>
+        <v>0.000937822376441902</v>
       </c>
     </row>
     <row r="882">
@@ -16249,7 +16249,7 @@
         <v>1</v>
       </c>
       <c r="D883">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="884">
@@ -16267,7 +16267,7 @@
         <v>1</v>
       </c>
       <c r="D884">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="885">
@@ -16429,7 +16429,7 @@
         <v>1</v>
       </c>
       <c r="D893">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="894">
@@ -16645,7 +16645,7 @@
         <v>1</v>
       </c>
       <c r="D905">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="906">
@@ -16789,7 +16789,7 @@
         <v>1</v>
       </c>
       <c r="D913">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="914">
@@ -16807,7 +16807,7 @@
         <v>1</v>
       </c>
       <c r="D914">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="915">
@@ -16825,7 +16825,7 @@
         <v>1</v>
       </c>
       <c r="D915">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="916">
@@ -16843,7 +16843,7 @@
         <v>1</v>
       </c>
       <c r="D916">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="917">
@@ -16951,7 +16951,7 @@
         <v>1</v>
       </c>
       <c r="D922">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="923">
@@ -16969,7 +16969,7 @@
         <v>1</v>
       </c>
       <c r="D923">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="924">
@@ -17005,7 +17005,7 @@
         <v>10</v>
       </c>
       <c r="D925">
-        <v>0.0009378223764419019</v>
+        <v>0.000937822376441902</v>
       </c>
     </row>
     <row r="926">
@@ -17023,7 +17023,7 @@
         <v>1</v>
       </c>
       <c r="D926">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="927">
@@ -17077,7 +17077,7 @@
         <v>1</v>
       </c>
       <c r="D929">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="930">
@@ -17113,7 +17113,7 @@
         <v>1</v>
       </c>
       <c r="D931">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="932">
@@ -17131,7 +17131,7 @@
         <v>1</v>
       </c>
       <c r="D932">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="933">
@@ -17149,7 +17149,7 @@
         <v>1</v>
       </c>
       <c r="D933">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="934">
@@ -17167,7 +17167,7 @@
         <v>1</v>
       </c>
       <c r="D934">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="935">
@@ -17239,7 +17239,7 @@
         <v>1</v>
       </c>
       <c r="D938">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="939">
@@ -17293,7 +17293,7 @@
         <v>1</v>
       </c>
       <c r="D941">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="942">
@@ -17401,7 +17401,7 @@
         <v>1</v>
       </c>
       <c r="D947">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="948">
@@ -17419,7 +17419,7 @@
         <v>1</v>
       </c>
       <c r="D948">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="949">
@@ -17430,14 +17430,14 @@
       </c>
       <c r="B949" t="inlineStr">
         <is>
-          <t>Amaxac De Guerero</t>
+          <t>Amaxac De Guerrero</t>
         </is>
       </c>
       <c r="C949">
         <v>1</v>
       </c>
       <c r="D949">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="950">
@@ -17473,7 +17473,7 @@
         <v>1</v>
       </c>
       <c r="D951">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="952">
@@ -17491,7 +17491,7 @@
         <v>1</v>
       </c>
       <c r="D952">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="953">
@@ -17509,7 +17509,7 @@
         <v>1</v>
       </c>
       <c r="D953">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="954">
@@ -17527,7 +17527,7 @@
         <v>1</v>
       </c>
       <c r="D954">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="955">
@@ -17545,7 +17545,7 @@
         <v>1</v>
       </c>
       <c r="D955">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="956">
@@ -17563,7 +17563,7 @@
         <v>1</v>
       </c>
       <c r="D956">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="957">
@@ -17599,7 +17599,7 @@
         <v>1</v>
       </c>
       <c r="D958">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="959">
@@ -17617,7 +17617,7 @@
         <v>1</v>
       </c>
       <c r="D959">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="960">
@@ -17653,7 +17653,7 @@
         <v>1</v>
       </c>
       <c r="D961">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="962">
@@ -17743,7 +17743,7 @@
         <v>1</v>
       </c>
       <c r="D966">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="967">
@@ -17779,7 +17779,7 @@
         <v>1</v>
       </c>
       <c r="D968">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="969">
@@ -17815,7 +17815,7 @@
         <v>1</v>
       </c>
       <c r="D970">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="971">
@@ -17869,7 +17869,7 @@
         <v>1</v>
       </c>
       <c r="D973">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="974">
@@ -17887,7 +17887,7 @@
         <v>1</v>
       </c>
       <c r="D974">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="975">
@@ -17941,7 +17941,7 @@
         <v>1</v>
       </c>
       <c r="D977">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="978">
@@ -17977,7 +17977,7 @@
         <v>1</v>
       </c>
       <c r="D979">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="980">
@@ -18031,7 +18031,7 @@
         <v>1</v>
       </c>
       <c r="D982">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="983">
@@ -18067,7 +18067,7 @@
         <v>1</v>
       </c>
       <c r="D984">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="985">
@@ -18085,7 +18085,7 @@
         <v>1</v>
       </c>
       <c r="D985">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="986">
@@ -18103,7 +18103,7 @@
         <v>1</v>
       </c>
       <c r="D986">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="987">
@@ -18193,7 +18193,7 @@
         <v>1</v>
       </c>
       <c r="D991">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="992">
@@ -18301,7 +18301,7 @@
         <v>1</v>
       </c>
       <c r="D997">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="998">
@@ -18373,7 +18373,7 @@
         <v>1</v>
       </c>
       <c r="D1001">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1002">
@@ -18391,7 +18391,7 @@
         <v>1</v>
       </c>
       <c r="D1002">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1003">
@@ -18409,7 +18409,7 @@
         <v>1</v>
       </c>
       <c r="D1003">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1004">
@@ -18445,7 +18445,7 @@
         <v>1</v>
       </c>
       <c r="D1005">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1006">
@@ -18517,7 +18517,7 @@
         <v>1</v>
       </c>
       <c r="D1009">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1010">
@@ -18535,7 +18535,7 @@
         <v>1</v>
       </c>
       <c r="D1010">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1011">
@@ -18571,7 +18571,7 @@
         <v>1</v>
       </c>
       <c r="D1012">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1013">
@@ -18679,7 +18679,7 @@
         <v>1</v>
       </c>
       <c r="D1018">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1019">
@@ -18805,7 +18805,7 @@
         <v>1</v>
       </c>
       <c r="D1025">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1026">
@@ -18859,7 +18859,7 @@
         <v>1</v>
       </c>
       <c r="D1028">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1029">
@@ -18877,7 +18877,7 @@
         <v>1</v>
       </c>
       <c r="D1029">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1030">
@@ -18913,7 +18913,7 @@
         <v>1</v>
       </c>
       <c r="D1031">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1032">
@@ -18967,7 +18967,7 @@
         <v>1</v>
       </c>
       <c r="D1034">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1035">
@@ -18985,7 +18985,7 @@
         <v>1</v>
       </c>
       <c r="D1035">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1036">
@@ -19003,7 +19003,7 @@
         <v>1</v>
       </c>
       <c r="D1036">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1037">
@@ -19039,7 +19039,7 @@
         <v>1</v>
       </c>
       <c r="D1038">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1039">
@@ -19075,7 +19075,7 @@
         <v>1</v>
       </c>
       <c r="D1040">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1041">
@@ -19093,7 +19093,7 @@
         <v>1</v>
       </c>
       <c r="D1041">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1042">
@@ -19111,7 +19111,7 @@
         <v>1</v>
       </c>
       <c r="D1042">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1043">
@@ -19129,7 +19129,7 @@
         <v>1</v>
       </c>
       <c r="D1043">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1044">
@@ -19165,7 +19165,7 @@
         <v>10</v>
       </c>
       <c r="D1045">
-        <v>0.0009378223764419019</v>
+        <v>0.000937822376441902</v>
       </c>
     </row>
     <row r="1046">
@@ -19219,7 +19219,7 @@
         <v>1</v>
       </c>
       <c r="D1048">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1049">
@@ -19255,7 +19255,7 @@
         <v>1</v>
       </c>
       <c r="D1050">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1051">
@@ -19273,7 +19273,7 @@
         <v>1</v>
       </c>
       <c r="D1051">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1052">
@@ -19309,7 +19309,7 @@
         <v>1</v>
       </c>
       <c r="D1053">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1054">
@@ -19327,7 +19327,7 @@
         <v>1</v>
       </c>
       <c r="D1054">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1055">
@@ -19381,7 +19381,7 @@
         <v>1</v>
       </c>
       <c r="D1057">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1058">
@@ -19399,7 +19399,7 @@
         <v>1</v>
       </c>
       <c r="D1058">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1059">
@@ -19453,7 +19453,7 @@
         <v>1</v>
       </c>
       <c r="D1061">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1062">
@@ -19471,7 +19471,7 @@
         <v>1</v>
       </c>
       <c r="D1062">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1063">
@@ -19489,7 +19489,7 @@
         <v>1</v>
       </c>
       <c r="D1063">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1064">
@@ -19525,7 +19525,7 @@
         <v>1</v>
       </c>
       <c r="D1065">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1066">
@@ -19543,7 +19543,7 @@
         <v>1</v>
       </c>
       <c r="D1066">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1067">
@@ -19579,7 +19579,7 @@
         <v>1</v>
       </c>
       <c r="D1068">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1069">
@@ -19597,7 +19597,7 @@
         <v>1</v>
       </c>
       <c r="D1069">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1070">
@@ -19633,7 +19633,7 @@
         <v>1</v>
       </c>
       <c r="D1071">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1072">
@@ -19651,7 +19651,7 @@
         <v>1</v>
       </c>
       <c r="D1072">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1073">
@@ -19687,7 +19687,7 @@
         <v>1</v>
       </c>
       <c r="D1074">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1075">
@@ -19957,7 +19957,7 @@
         <v>1</v>
       </c>
       <c r="D1089">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1090">
@@ -20083,7 +20083,7 @@
         <v>1</v>
       </c>
       <c r="D1096">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1097">
@@ -20263,7 +20263,7 @@
         <v>1</v>
       </c>
       <c r="D1106">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1107">
@@ -20425,7 +20425,7 @@
         <v>1</v>
       </c>
       <c r="D1115">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1116">
@@ -20443,7 +20443,7 @@
         <v>1</v>
       </c>
       <c r="D1116">
-        <v>9.378223764419019E-05</v>
+        <v>9.378223764419021E-05</v>
       </c>
     </row>
     <row r="1117">
